--- a/docs/nganhang/bank_statement_summary.xlsx
+++ b/docs/nganhang/bank_statement_summary.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>filename</t>
   </si>
@@ -46,250 +48,249 @@
     <t>closing_balance</t>
   </si>
   <si>
-    <t>Đã quét_20260309-0005-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2245-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0254-01.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2249-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0006-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2251-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0223-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2253-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2256-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0226-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2258-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0233-01.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2336-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2338-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2339-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0243-01.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2341-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2342-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0249-01.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2344-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2345-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2346-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2347-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2349-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2351-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2352-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2354-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2356-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2358-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260308-2359-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0001-1.png</t>
-  </si>
-  <si>
-    <t>Đã quét_20260309-0003-1.png</t>
+    <t xml:space="preserve">Đã quét_20260309-0005-1.png</t>
   </si>
   <si>
     <t>ACB</t>
   </si>
   <si>
+    <t>999955666868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONG TY TNHH MTV HUY VU</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/01/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2245-1.png</t>
+  </si>
+  <si>
     <t>BIDV</t>
   </si>
   <si>
+    <t>6200299852</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0254-01.png</t>
+  </si>
+  <si>
     <t>Sacombank</t>
   </si>
   <si>
-    <t>999955666868</t>
-  </si>
-  <si>
-    <t>6200299852</t>
-  </si>
-  <si>
     <t>040019911911</t>
   </si>
   <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2249-1.png</t>
+  </si>
+  <si>
+    <t>01/02/2023</t>
+  </si>
+  <si>
+    <t>28/02/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0006-1.png</t>
+  </si>
+  <si>
+    <t>01/02/2024</t>
+  </si>
+  <si>
+    <t>29/02/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2251-1.png</t>
+  </si>
+  <si>
+    <t>01/03/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0223-1.png</t>
+  </si>
+  <si>
+    <t>01/03/2024</t>
+  </si>
+  <si>
+    <t>31/03/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2253-1.png</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/04/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2256-1.png</t>
+  </si>
+  <si>
+    <t>01/05/2023</t>
+  </si>
+  <si>
+    <t>31/05/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0226-1.png</t>
+  </si>
+  <si>
+    <t>01/05/2024</t>
+  </si>
+  <si>
+    <t>31/05/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2258-1.png</t>
+  </si>
+  <si>
+    <t>01/06/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0233-01.png</t>
+  </si>
+  <si>
+    <t>01/06/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2336-1.png</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>31/07/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2338-1.png</t>
+  </si>
+  <si>
+    <t>01/08/2023</t>
+  </si>
+  <si>
+    <t>31/08/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2339-1.png</t>
+  </si>
+  <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0243-01.png</t>
+  </si>
+  <si>
+    <t>01/09/2024</t>
+  </si>
+  <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2341-1.png</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/10/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2342-1.png</t>
+  </si>
+  <si>
+    <t>01/11/2023</t>
+  </si>
+  <si>
+    <t>30/11/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0249-01.png</t>
+  </si>
+  <si>
+    <t>01/11/2024</t>
+  </si>
+  <si>
+    <t>30/11/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2344-1.png</t>
+  </si>
+  <si>
+    <t>01/12/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2345-1.png</t>
+  </si>
+  <si>
     <t>040021224301</t>
   </si>
   <si>
-    <t>CONG TY TNHH MTV HUY VU</t>
-  </si>
-  <si>
-    <t>01/01/2023</t>
-  </si>
-  <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>01/02/2023</t>
-  </si>
-  <si>
-    <t>01/02/2024</t>
-  </si>
-  <si>
-    <t>01/03/2023</t>
-  </si>
-  <si>
-    <t>01/03/2024</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>01/05/2023</t>
-  </si>
-  <si>
-    <t>01/05/2024</t>
-  </si>
-  <si>
-    <t>01/06/2023</t>
-  </si>
-  <si>
-    <t>01/06/2024</t>
-  </si>
-  <si>
-    <t>01/07/2023</t>
-  </si>
-  <si>
-    <t>01/08/2023</t>
-  </si>
-  <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
-    <t>01/09/2024</t>
-  </si>
-  <si>
-    <t>01/10/2023</t>
-  </si>
-  <si>
-    <t>01/11/2023</t>
-  </si>
-  <si>
-    <t>01/11/2024</t>
-  </si>
-  <si>
-    <t>01/12/2023</t>
-  </si>
-  <si>
-    <t>31/01/2023</t>
-  </si>
-  <si>
-    <t>31/12/2023</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>28/02/2023</t>
-  </si>
-  <si>
-    <t>29/02/2024</t>
-  </si>
-  <si>
-    <t>31/03/2023</t>
-  </si>
-  <si>
-    <t>31/03/2024</t>
-  </si>
-  <si>
-    <t>30/04/2023</t>
-  </si>
-  <si>
-    <t>31/05/2023</t>
-  </si>
-  <si>
-    <t>31/05/2024</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>31/07/2023</t>
-  </si>
-  <si>
-    <t>31/08/2023</t>
-  </si>
-  <si>
-    <t>30/09/2023</t>
-  </si>
-  <si>
-    <t>30/09/2024</t>
-  </si>
-  <si>
-    <t>31/10/2023</t>
-  </si>
-  <si>
-    <t>30/11/2023</t>
-  </si>
-  <si>
-    <t>30/11/2024</t>
+    <t xml:space="preserve">Đã quét_20260308-2346-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2347-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2349-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2351-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2352-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2354-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2356-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2358-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260308-2359-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0001-1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã quét_20260309-0003-1.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -303,28 +304,33 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -370,13 +376,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -404,13 +410,13 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -607,12 +613,242 @@
 </a:theme>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="28.421875"/>
+    <col bestFit="1" min="2" max="2" width="11.00390625"/>
+    <col bestFit="1" min="3" max="3" width="15.57421875"/>
+    <col bestFit="1" min="4" max="4" width="25.6640625"/>
+    <col bestFit="1" min="5" max="6" width="10.61328125"/>
+    <col bestFit="1" min="7" max="7" width="15.57421875"/>
+    <col bestFit="1" min="8" max="8" width="10.23046875"/>
+    <col bestFit="1" min="9" max="9" width="10.7109375"/>
+    <col bestFit="1" min="10" max="10" width="14.421875"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -644,24 +880,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>307434</v>
@@ -676,717 +912,717 @@
         <v>398697</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G3">
         <v>5949606</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="G4">
         <v>521610456</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>196908775</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>86602341</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>13960294</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>37741605</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G9">
         <v>1354913</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G10">
         <v>70254477</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" t="s">
-        <v>58</v>
-      </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="G11">
         <v>16080668</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
-      </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="G12">
         <v>20234487</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G13">
         <v>18467617</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>166638776</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>1946813</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G16">
         <v>1570511</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="G17">
         <v>12306623</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
         <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>46091342</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G19">
         <v>1004232</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G20">
         <v>121223828</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G21">
         <v>51566267</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
         <v>48</v>
       </c>
-      <c r="D22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" t="s">
         <v>54</v>
       </c>
-      <c r="F24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
         <v>56</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
         <v>76</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
         <v>59</v>
       </c>
-      <c r="F27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" t="s">
-        <v>63</v>
-      </c>
       <c r="F30" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1401,24 +1637,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
         <v>65</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1433,24 +1669,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1465,24 +1701,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1498,6 +1734,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>